--- a/Data/FlightPlan/FPL_02SEP26.xlsx
+++ b/Data/FlightPlan/FPL_02SEP26.xlsx
@@ -827,225 +827,228 @@
     <t>VN-A630</t>
   </si>
   <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
     <t>05:20</t>
   </si>
   <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>CTU</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
     <t>14:15</t>
   </si>
   <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>CTU</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
     <t>VN-A651</t>
   </si>
   <si>
@@ -1142,9 +1145,6 @@
     <t>06:55</t>
   </si>
   <si>
-    <t>20:50</t>
-  </si>
-  <si>
     <t>VN-A671</t>
   </si>
   <si>
@@ -1208,6 +1208,9 @@
     <t>04:05</t>
   </si>
   <si>
+    <t>07:24</t>
+  </si>
+  <si>
     <t>VN-A698</t>
   </si>
   <si>
@@ -1250,7 +1253,7 @@
     <t>Total Record(s): 456</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 02, 2026 01:38</t>
+    <t xml:space="preserve">Generated on  Sep 02, 2026 03:45</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -7450,7 +7453,7 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>1624</v>
+        <v>260</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
@@ -7466,13 +7469,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>29</v>
+        <v>242</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7483,7 +7486,7 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>625</v>
+        <v>261</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
@@ -7496,16 +7499,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>29</v>
+        <v>242</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7516,7 +7519,7 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>887</v>
+        <v>335</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
@@ -7532,13 +7535,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>273</v>
+        <v>28</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7549,7 +7552,7 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>882</v>
+        <v>766</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
@@ -7562,16 +7565,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7582,7 +7585,7 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>312</v>
+        <v>767</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
@@ -7595,16 +7598,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>274</v>
+        <v>88</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7615,7 +7618,7 @@
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
@@ -7628,50 +7631,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>274</v>
+        <v>88</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>57</v>
+        <v>204</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c t="s" r="A201" s="6">
-        <v>13</v>
-      </c>
-      <c r="B201" s="7">
-        <v>1652</v>
-      </c>
-      <c t="s" r="C201" s="7">
-        <v>14</v>
-      </c>
+      <c r="A201" s="6"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="7"/>
       <c r="D201" s="7"/>
-      <c t="s" r="E201" s="7">
-        <v>271</v>
-      </c>
-      <c r="F201" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G201" s="8">
-        <v>39</v>
-      </c>
-      <c t="s" r="H201" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I201" s="7">
-        <v>171</v>
-      </c>
-      <c t="s" r="J201" s="7">
-        <v>123</v>
-      </c>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="8"/>
+      <c r="H201" s="8"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="7"/>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
@@ -7681,14 +7666,14 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>1655</v>
+        <v>1506</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7697,29 +7682,47 @@
         <v>29</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>34</v>
+        <v>273</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
-      <c r="A203" s="6"/>
-      <c r="B203" s="7"/>
-      <c r="C203" s="7"/>
+      <c t="s" r="A203" s="6">
+        <v>13</v>
+      </c>
+      <c r="B203" s="7">
+        <v>503</v>
+      </c>
+      <c t="s" r="C203" s="7">
+        <v>14</v>
+      </c>
       <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
-      <c r="G203" s="8"/>
-      <c r="H203" s="8"/>
-      <c r="I203" s="7"/>
-      <c r="J203" s="7"/>
+      <c t="s" r="E203" s="7">
+        <v>272</v>
+      </c>
+      <c r="F203" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G203" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H203" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I203" s="7">
+        <v>94</v>
+      </c>
+      <c t="s" r="J203" s="7">
+        <v>103</v>
+      </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c r="M203" s="7"/>
@@ -7729,14 +7732,14 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>1506</v>
+        <v>524</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7748,10 +7751,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7762,14 +7765,14 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7781,10 +7784,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7795,14 +7798,14 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7814,10 +7817,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7828,14 +7831,14 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>507</v>
+        <v>405</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7844,13 +7847,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7861,29 +7864,29 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>510</v>
+        <v>406</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7894,29 +7897,29 @@
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>405</v>
+        <v>783</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
+        <v>272</v>
+      </c>
+      <c r="F209" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G209" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H209" s="8">
+        <v>51</v>
+      </c>
+      <c t="s" r="I209" s="7">
         <v>275</v>
       </c>
-      <c r="F209" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G209" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H209" s="8">
-        <v>174</v>
-      </c>
-      <c t="s" r="I209" s="7">
-        <v>119</v>
-      </c>
       <c t="s" r="J209" s="7">
-        <v>277</v>
+        <v>193</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7927,63 +7930,45 @@
         <v>13</v>
       </c>
       <c r="B210" s="7">
-        <v>406</v>
+        <v>784</v>
       </c>
       <c t="s" r="C210" s="7">
         <v>14</v>
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>177</v>
+        <v>36</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c t="s" r="A211" s="6">
-        <v>13</v>
-      </c>
-      <c r="B211" s="7">
-        <v>783</v>
-      </c>
-      <c t="s" r="C211" s="7">
-        <v>14</v>
-      </c>
+      <c r="A211" s="6"/>
+      <c r="B211" s="7"/>
+      <c r="C211" s="7"/>
       <c r="D211" s="7"/>
-      <c t="s" r="E211" s="7">
-        <v>275</v>
-      </c>
-      <c r="F211" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G211" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H211" s="8">
-        <v>51</v>
-      </c>
-      <c t="s" r="I211" s="7">
-        <v>278</v>
-      </c>
-      <c t="s" r="J211" s="7">
-        <v>193</v>
-      </c>
+      <c r="E211" s="7"/>
+      <c r="F211" s="7"/>
+      <c r="G211" s="8"/>
+      <c r="H211" s="8"/>
+      <c r="I211" s="7"/>
+      <c r="J211" s="7"/>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c r="M211" s="7"/>
@@ -7993,45 +7978,63 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>784</v>
+        <v>1625</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c r="M212" s="7"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c r="A213" s="6"/>
-      <c r="B213" s="7"/>
-      <c r="C213" s="7"/>
+      <c t="s" r="A213" s="6">
+        <v>13</v>
+      </c>
+      <c r="B213" s="7">
+        <v>825</v>
+      </c>
+      <c t="s" r="C213" s="7">
+        <v>14</v>
+      </c>
       <c r="D213" s="7"/>
-      <c r="E213" s="7"/>
-      <c r="F213" s="7"/>
-      <c r="G213" s="8"/>
-      <c r="H213" s="8"/>
-      <c r="I213" s="7"/>
-      <c r="J213" s="7"/>
+      <c t="s" r="E213" s="7">
+        <v>276</v>
+      </c>
+      <c r="F213" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G213" s="8">
+        <v>39</v>
+      </c>
+      <c t="s" r="H213" s="8">
+        <v>258</v>
+      </c>
+      <c t="s" r="I213" s="7">
+        <v>224</v>
+      </c>
+      <c t="s" r="J213" s="7">
+        <v>278</v>
+      </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c r="M213" s="7"/>
@@ -8041,29 +8044,29 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>1625</v>
+        <v>826</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>29</v>
+        <v>258</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>280</v>
+        <v>63</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>252</v>
+        <v>76</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8074,29 +8077,29 @@
         <v>13</v>
       </c>
       <c r="B215" s="7">
-        <v>825</v>
+        <v>310</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
+        <v>276</v>
+      </c>
+      <c r="F215" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G215" s="8">
+        <v>39</v>
+      </c>
+      <c t="s" r="H215" s="8">
         <v>279</v>
       </c>
-      <c r="F215" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G215" s="8">
-        <v>39</v>
-      </c>
-      <c t="s" r="H215" s="8">
-        <v>258</v>
-      </c>
       <c t="s" r="I215" s="7">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>281</v>
+        <v>120</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8107,29 +8110,29 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>826</v>
+        <v>309</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
+        <v>276</v>
+      </c>
+      <c r="F216" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G216" s="8">
         <v>279</v>
       </c>
-      <c r="F216" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G216" s="8">
-        <v>258</v>
-      </c>
       <c t="s" r="H216" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>76</v>
+        <v>212</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8140,14 +8143,14 @@
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>310</v>
+        <v>1216</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8156,13 +8159,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>241</v>
+        <v>147</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8173,63 +8176,45 @@
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>309</v>
+        <v>1217</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c r="M218" s="7"/>
     </row>
     <row r="219" ht="14.25" customHeight="1">
-      <c t="s" r="A219" s="6">
-        <v>13</v>
-      </c>
-      <c r="B219" s="7">
-        <v>1216</v>
-      </c>
-      <c t="s" r="C219" s="7">
-        <v>14</v>
-      </c>
+      <c r="A219" s="6"/>
+      <c r="B219" s="7"/>
+      <c r="C219" s="7"/>
       <c r="D219" s="7"/>
-      <c t="s" r="E219" s="7">
-        <v>279</v>
-      </c>
-      <c r="F219" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G219" s="8">
-        <v>39</v>
-      </c>
-      <c t="s" r="H219" s="8">
-        <v>142</v>
-      </c>
-      <c t="s" r="I219" s="7">
-        <v>147</v>
-      </c>
-      <c t="s" r="J219" s="7">
-        <v>122</v>
-      </c>
+      <c r="E219" s="7"/>
+      <c r="F219" s="7"/>
+      <c r="G219" s="8"/>
+      <c r="H219" s="8"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="7"/>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c r="M219" s="7"/>
@@ -8239,45 +8224,63 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>1217</v>
+        <v>1624</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>142</v>
+        <v>39</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>229</v>
+        <v>124</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c r="M220" s="7"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
-      <c r="A221" s="6"/>
-      <c r="B221" s="7"/>
-      <c r="C221" s="7"/>
+      <c t="s" r="A221" s="6">
+        <v>13</v>
+      </c>
+      <c r="B221" s="7">
+        <v>625</v>
+      </c>
+      <c t="s" r="C221" s="7">
+        <v>14</v>
+      </c>
       <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
-      <c r="F221" s="7"/>
-      <c r="G221" s="8"/>
-      <c r="H221" s="8"/>
-      <c r="I221" s="7"/>
-      <c r="J221" s="7"/>
+      <c t="s" r="E221" s="7">
+        <v>280</v>
+      </c>
+      <c r="F221" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G221" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H221" s="8">
+        <v>39</v>
+      </c>
+      <c t="s" r="I221" s="7">
+        <v>37</v>
+      </c>
+      <c t="s" r="J221" s="7">
+        <v>82</v>
+      </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
@@ -8287,14 +8290,14 @@
         <v>13</v>
       </c>
       <c r="B222" s="7">
-        <v>260</v>
+        <v>803</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8303,13 +8306,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>242</v>
+        <v>105</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>252</v>
+        <v>86</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8320,29 +8323,29 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>261</v>
+        <v>804</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
+        <v>280</v>
+      </c>
+      <c r="F223" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G223" s="8">
+        <v>105</v>
+      </c>
+      <c t="s" r="H223" s="8">
+        <v>39</v>
+      </c>
+      <c t="s" r="I223" s="7">
         <v>282</v>
       </c>
-      <c r="F223" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G223" s="8">
-        <v>242</v>
-      </c>
-      <c t="s" r="H223" s="8">
-        <v>39</v>
-      </c>
-      <c t="s" r="I223" s="7">
-        <v>134</v>
-      </c>
       <c t="s" r="J223" s="7">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8353,14 +8356,14 @@
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>335</v>
+        <v>254</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8369,13 +8372,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8386,29 +8389,29 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>766</v>
+        <v>255</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>166</v>
+        <v>39</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8419,29 +8422,29 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>767</v>
+        <v>1318</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>166</v>
+        <v>39</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>88</v>
+        <v>279</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8452,29 +8455,29 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>338</v>
+        <v>1319</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>88</v>
+        <v>279</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>46</v>
+        <v>247</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8507,7 +8510,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8519,7 +8522,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>190</v>
@@ -8540,7 +8543,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8573,7 +8576,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8606,7 +8609,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8618,7 +8621,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>44</v>
@@ -8639,7 +8642,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8672,7 +8675,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8687,7 +8690,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8705,7 +8708,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8717,7 +8720,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>148</v>
@@ -8738,7 +8741,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8750,7 +8753,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>237</v>
@@ -8786,7 +8789,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8819,7 +8822,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8852,7 +8855,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8867,7 +8870,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8885,7 +8888,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8918,7 +8921,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8951,7 +8954,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8999,7 +9002,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9011,7 +9014,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>197</v>
@@ -9032,7 +9035,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9044,7 +9047,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>85</v>
@@ -9065,7 +9068,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9077,10 +9080,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9098,7 +9101,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9131,7 +9134,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9164,7 +9167,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9197,7 +9200,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9209,7 +9212,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>177</v>
@@ -9230,7 +9233,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9263,7 +9266,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9311,7 +9314,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9323,7 +9326,7 @@
         <v>118</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>52</v>
@@ -9344,7 +9347,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9356,10 +9359,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9377,7 +9380,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9386,7 +9389,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>103</v>
@@ -9410,22 +9413,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9443,7 +9446,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9476,7 +9479,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9509,7 +9512,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9524,7 +9527,7 @@
         <v>212</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9542,7 +9545,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9557,7 +9560,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9590,7 +9593,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9623,7 +9626,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9656,7 +9659,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9668,7 +9671,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>167</v>
@@ -9689,7 +9692,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9722,7 +9725,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9734,10 +9737,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9770,7 +9773,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9779,7 +9782,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>103</v>
@@ -9803,13 +9806,13 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>39</v>
@@ -9818,7 +9821,7 @@
         <v>200</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9836,7 +9839,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9851,7 +9854,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9869,7 +9872,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9884,7 +9887,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9902,7 +9905,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9935,7 +9938,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10097,7 +10100,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10160,7 +10163,7 @@
         <v>142</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>79</v>
@@ -10229,7 +10232,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10274,7 +10277,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>181</v>
@@ -10523,7 +10526,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10589,7 +10592,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10769,7 +10772,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10880,7 +10883,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>43</v>
@@ -11210,7 +11213,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11486,7 +11489,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>273</v>
+        <v>345</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>226</v>
@@ -11585,7 +11588,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>247</v>
@@ -11621,7 +11624,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11633,7 +11636,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>175</v>
@@ -11654,7 +11657,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11687,7 +11690,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11720,7 +11723,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11753,7 +11756,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11786,7 +11789,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11834,7 +11837,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11846,7 +11849,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>220</v>
@@ -11867,7 +11870,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11900,7 +11903,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11933,7 +11936,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11981,7 +11984,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11993,7 +11996,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>343</v>
@@ -12014,7 +12017,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12047,7 +12050,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12080,7 +12083,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12113,7 +12116,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12122,7 +12125,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>66</v>
@@ -12146,19 +12149,19 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>161</v>
@@ -12194,7 +12197,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12227,7 +12230,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12260,7 +12263,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12272,7 +12275,7 @@
         <v>174</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>159</v>
@@ -12293,7 +12296,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12326,7 +12329,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12335,10 +12338,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>224</v>
@@ -12374,7 +12377,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12386,7 +12389,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>208</v>
@@ -12407,7 +12410,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12440,7 +12443,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12449,7 +12452,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I358" s="7">
         <v>27</v>
@@ -12473,13 +12476,13 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>16</v>
@@ -12506,7 +12509,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12554,7 +12557,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12569,7 +12572,7 @@
         <v>196</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12587,7 +12590,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12599,7 +12602,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>86</v>
@@ -12620,7 +12623,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12653,7 +12656,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12662,7 +12665,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>119</v>
@@ -12686,19 +12689,19 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>129</v>
@@ -12719,7 +12722,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12728,7 +12731,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>110</v>
@@ -12752,22 +12755,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12800,7 +12803,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12833,7 +12836,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12866,7 +12869,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12875,7 +12878,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>182</v>
@@ -12899,13 +12902,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
@@ -12932,7 +12935,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12941,7 +12944,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>319</v>
@@ -12965,22 +12968,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12998,7 +13001,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13013,7 +13016,7 @@
         <v>244</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13046,7 +13049,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13055,13 +13058,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>220</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>273</v>
+        <v>345</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13079,13 +13082,13 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>39</v>
@@ -13127,7 +13130,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13139,7 +13142,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>208</v>
@@ -13160,7 +13163,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13193,7 +13196,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13205,10 +13208,10 @@
         <v>174</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>273</v>
+        <v>345</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13226,7 +13229,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13238,7 +13241,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>184</v>
@@ -13259,7 +13262,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13292,7 +13295,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13304,10 +13307,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13340,7 +13343,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13373,7 +13376,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13406,7 +13409,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13439,7 +13442,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13472,7 +13475,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13481,7 +13484,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>90</v>
@@ -13505,13 +13508,13 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
@@ -13538,7 +13541,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13571,7 +13574,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13583,7 +13586,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>222</v>
@@ -13619,7 +13622,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13652,7 +13655,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13685,7 +13688,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13718,7 +13721,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13751,7 +13754,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13763,10 +13766,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13799,7 +13802,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -13808,10 +13811,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>124</v>
@@ -13832,13 +13835,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>39</v>
@@ -13865,7 +13868,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -13874,7 +13877,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>27</v>
@@ -13898,13 +13901,13 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>39</v>
@@ -13931,7 +13934,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -13964,7 +13967,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -13976,10 +13979,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13997,7 +14000,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -14030,7 +14033,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14042,7 +14045,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>148</v>
@@ -14078,7 +14081,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -14093,7 +14096,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14111,7 +14114,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14126,7 +14129,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14144,7 +14147,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14177,7 +14180,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14210,7 +14213,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14243,7 +14246,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -14258,7 +14261,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14291,7 +14294,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14300,13 +14303,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I419" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14324,13 +14327,13 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>39</v>
@@ -14350,14 +14353,14 @@
         <v>13</v>
       </c>
       <c r="B421" s="7">
-        <v>803</v>
+        <v>887</v>
       </c>
       <c t="s" r="C421" s="7">
         <v>14</v>
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14366,13 +14369,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>116</v>
+        <v>345</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14383,29 +14386,29 @@
         <v>13</v>
       </c>
       <c r="B422" s="7">
-        <v>804</v>
+        <v>882</v>
       </c>
       <c t="s" r="C422" s="7">
         <v>14</v>
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>308</v>
+        <v>64</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14416,14 +14419,14 @@
         <v>13</v>
       </c>
       <c r="B423" s="7">
-        <v>254</v>
+        <v>312</v>
       </c>
       <c t="s" r="C423" s="7">
         <v>14</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14432,13 +14435,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>101</v>
+        <v>279</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>241</v>
+        <v>56</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14449,29 +14452,29 @@
         <v>13</v>
       </c>
       <c r="B424" s="7">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c t="s" r="C424" s="7">
         <v>14</v>
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>101</v>
+        <v>279</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>377</v>
+        <v>170</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14482,14 +14485,14 @@
         <v>13</v>
       </c>
       <c r="B425" s="7">
-        <v>1318</v>
+        <v>1652</v>
       </c>
       <c t="s" r="C425" s="7">
         <v>14</v>
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14498,13 +14501,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>171</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14515,29 +14518,29 @@
         <v>13</v>
       </c>
       <c r="B426" s="7">
-        <v>1319</v>
+        <v>1655</v>
       </c>
       <c t="s" r="C426" s="7">
         <v>14</v>
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14651,7 +14654,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14711,7 +14714,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="I432" s="7">
         <v>57</v>
@@ -14741,7 +14744,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>16</v>
@@ -14798,7 +14801,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14831,7 +14834,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14897,7 +14900,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15122,7 +15125,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>245</v>
@@ -15731,7 +15734,7 @@
         <v>339</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>377</v>
+        <v>284</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
@@ -15761,7 +15764,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J467" s="7">
         <v>37</v>
@@ -15809,7 +15812,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>190</v>
@@ -15875,7 +15878,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>146</v>
@@ -15911,7 +15914,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>377</v>
+        <v>284</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -15941,7 +15944,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J473" s="7">
         <v>154</v>
@@ -15992,7 +15995,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -16055,7 +16058,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J477" s="7">
         <v>183</v>
@@ -16157,7 +16160,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16334,7 +16337,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>116</v>
@@ -16547,10 +16550,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="J493" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
@@ -16610,10 +16613,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H495" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I495" s="7">
-        <v>273</v>
+        <v>345</v>
       </c>
       <c t="s" r="J495" s="7">
         <v>119</v>
@@ -16640,7 +16643,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G496" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H496" s="8">
         <v>39</v>
@@ -16649,7 +16652,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
@@ -16892,10 +16895,10 @@
         <v>114</v>
       </c>
       <c t="s" r="I504" s="7">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c t="s" r="J504" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K504" s="7"/>
       <c r="L504" s="7"/>
@@ -16925,10 +16928,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I505" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J505" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K505" s="7"/>
       <c r="L505" s="7"/>
@@ -17006,7 +17009,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I508" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J508" s="7">
         <v>224</v>
@@ -17036,7 +17039,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H509" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I509" s="7">
         <v>115</v>
@@ -17066,7 +17069,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G510" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H510" s="8">
         <v>39</v>
@@ -17075,7 +17078,7 @@
         <v>240</v>
       </c>
       <c t="s" r="J510" s="7">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
@@ -17141,7 +17144,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J512" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K512" s="7"/>
       <c r="L512" s="7"/>
@@ -17174,7 +17177,7 @@
         <v>251</v>
       </c>
       <c t="s" r="J513" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
@@ -17226,7 +17229,9 @@
       </c>
       <c r="K515" s="7"/>
       <c r="L515" s="7"/>
-      <c r="M515" s="7"/>
+      <c t="s" r="M515" s="7">
+        <v>399</v>
+      </c>
     </row>
     <row r="516" ht="14.25" customHeight="1">
       <c t="s" r="A516" s="6">
@@ -17354,7 +17359,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F520" s="7">
         <v>321</v>
@@ -17387,7 +17392,7 @@
       </c>
       <c r="D521" s="7"/>
       <c t="s" r="E521" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F521" s="7">
         <v>321</v>
@@ -17402,7 +17407,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J521" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K521" s="7"/>
       <c r="L521" s="7"/>
@@ -17420,7 +17425,7 @@
       </c>
       <c r="D522" s="7"/>
       <c t="s" r="E522" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F522" s="7">
         <v>321</v>
@@ -17453,7 +17458,7 @@
       </c>
       <c r="D523" s="7"/>
       <c t="s" r="E523" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F523" s="7">
         <v>321</v>
@@ -17486,7 +17491,7 @@
       </c>
       <c r="D524" s="7"/>
       <c t="s" r="E524" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F524" s="7">
         <v>321</v>
@@ -17519,7 +17524,7 @@
       </c>
       <c r="D525" s="7"/>
       <c t="s" r="E525" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F525" s="7">
         <v>321</v>
@@ -17567,7 +17572,7 @@
       </c>
       <c r="D527" s="7"/>
       <c t="s" r="E527" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F527" s="7">
         <v>330</v>
@@ -17600,7 +17605,7 @@
       </c>
       <c r="D528" s="7"/>
       <c t="s" r="E528" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F528" s="7">
         <v>330</v>
@@ -17609,10 +17614,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H528" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="I528" s="7">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c t="s" r="J528" s="7">
         <v>159</v>
@@ -17633,13 +17638,13 @@
       </c>
       <c r="D529" s="7"/>
       <c t="s" r="E529" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F529" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G529" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="H529" s="8">
         <v>29</v>
@@ -17681,13 +17686,13 @@
       </c>
       <c r="D531" s="7"/>
       <c t="s" r="E531" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F531" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G531" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="H531" s="8">
         <v>51</v>
@@ -17729,7 +17734,7 @@
       </c>
       <c r="D533" s="7"/>
       <c t="s" r="E533" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F533" s="7">
         <v>330</v>
@@ -17741,7 +17746,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I533" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J533" s="7">
         <v>165</v>
@@ -17777,7 +17782,7 @@
       </c>
       <c r="D535" s="7"/>
       <c t="s" r="E535" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F535" s="7">
         <v>330</v>
@@ -17786,13 +17791,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H535" s="8">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c t="s" r="I535" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J535" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K535" s="7"/>
       <c r="L535" s="7"/>
@@ -17810,19 +17815,19 @@
       </c>
       <c r="D536" s="7"/>
       <c t="s" r="E536" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F536" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G536" s="8">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c t="s" r="H536" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I536" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="J536" s="7">
         <v>161</v>
@@ -17858,7 +17863,7 @@
       </c>
       <c r="D538" s="7"/>
       <c t="s" r="E538" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F538" s="7">
         <v>330</v>
@@ -17891,7 +17896,7 @@
       </c>
       <c r="D539" s="7"/>
       <c t="s" r="E539" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F539" s="7">
         <v>330</v>
@@ -17924,7 +17929,7 @@
       </c>
       <c r="D540" s="7"/>
       <c t="s" r="E540" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F540" s="7">
         <v>330</v>
@@ -17972,7 +17977,7 @@
       </c>
       <c r="D542" s="7"/>
       <c t="s" r="E542" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F542" s="7">
         <v>330</v>
@@ -17981,7 +17986,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H542" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="I542" s="7">
         <v>27</v>
@@ -18005,19 +18010,19 @@
       </c>
       <c r="D543" s="7"/>
       <c t="s" r="E543" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F543" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G543" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="H543" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I543" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J543" s="7">
         <v>150</v>
@@ -18053,13 +18058,13 @@
       </c>
       <c r="D545" s="7"/>
       <c t="s" r="E545" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F545" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G545" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="H545" s="8">
         <v>39</v>
@@ -18086,7 +18091,7 @@
       </c>
       <c r="D546" s="7"/>
       <c t="s" r="E546" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F546" s="7">
         <v>330</v>
@@ -18095,7 +18100,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H546" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="I546" s="7">
         <v>57</v>
@@ -18109,7 +18114,7 @@
     </row>
     <row r="547" ht="15.75" customHeight="1">
       <c t="s" r="A547" s="9">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B547" s="9"/>
       <c r="C547" s="9"/>
@@ -18129,7 +18134,7 @@
     <row r="548" ht="65.25" customHeight="1"/>
     <row r="549" ht="16.5" customHeight="1">
       <c t="s" r="A549" s="10">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B549" s="10"/>
       <c r="C549" s="10"/>
@@ -18142,7 +18147,7 @@
       <c r="J549" s="10"/>
       <c r="K549" s="10"/>
       <c t="s" r="L549" s="11">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M549" s="11"/>
       <c r="N549" s="11"/>
